--- a/Data/EXCEL/Transfer/salemon/202512/7583-salemon-202512.xlsx
+++ b/Data/EXCEL/Transfer/salemon/202512/7583-salemon-202512.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\202512\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\WORKSPACES\xls2xlsx\Transfer\202512\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D84CE295-0164-4BB1-8164-BE31B19F01C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AAAF9A74-F5CF-4FA2-B072-C3588B0D6C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8340" yWindow="930" windowWidth="26910" windowHeight="18975" xr2:uid="{720B035D-A1E0-46EC-85BA-D74A02A46670}"/>
+    <workbookView xWindow="0" yWindow="1740" windowWidth="17565" windowHeight="11295" xr2:uid="{63462A3E-915F-455D-A17A-FA9042440B5A}"/>
   </bookViews>
   <sheets>
     <sheet name="7583-salemon-202512" sheetId="2" r:id="rId1"/>
@@ -1258,20 +1258,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44C73A1B-C767-4D44-8FD0-7B5D1BF69BDE}">
-  <dimension ref="A1:Q31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{678F5488-C55E-4327-BB97-1AAA77814475}">
+  <dimension ref="A1:Q32"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.125" customWidth="1"/>
-    <col min="2" max="5" width="11.875" customWidth="1"/>
-    <col min="6" max="6" width="11.25" customWidth="1"/>
-    <col min="7" max="7" width="13" customWidth="1"/>
-    <col min="8" max="9" width="11.875" customWidth="1"/>
-    <col min="10" max="10" width="13.625" customWidth="1"/>
-    <col min="11" max="14" width="11.875" customWidth="1"/>
-    <col min="15" max="15" width="13.625" customWidth="1"/>
-    <col min="16" max="16" width="11.875" customWidth="1"/>
-    <col min="17" max="17" width="12.75" customWidth="1"/>
+    <col min="1" max="1" width="9.25" customWidth="1"/>
+    <col min="2" max="5" width="7.75" customWidth="1"/>
+    <col min="6" max="6" width="7.375" customWidth="1"/>
+    <col min="7" max="7" width="8.5" customWidth="1"/>
+    <col min="8" max="9" width="7.75" customWidth="1"/>
+    <col min="10" max="10" width="8.875" customWidth="1"/>
+    <col min="11" max="14" width="7.75" customWidth="1"/>
+    <col min="15" max="15" width="8.875" customWidth="1"/>
+    <col min="16" max="16" width="7.75" customWidth="1"/>
+    <col min="17" max="17" width="8.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.25">
@@ -1424,1279 +1424,1279 @@
     </row>
     <row r="5" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
-        <v>45962</v>
+        <v>45992</v>
       </c>
       <c r="B5" s="6">
+        <v>74.2</v>
+      </c>
+      <c r="C5" s="6">
+        <v>70.5</v>
+      </c>
+      <c r="D5" s="6">
         <v>75</v>
       </c>
-      <c r="C5" s="6">
-        <v>74.2</v>
-      </c>
-      <c r="D5" s="6">
-        <v>77.2</v>
-      </c>
       <c r="E5" s="6">
-        <v>71.5</v>
+        <v>67.8</v>
       </c>
       <c r="F5" s="7">
-        <v>-0.8</v>
+        <v>-3.7</v>
       </c>
       <c r="G5" s="7">
-        <v>-1.07</v>
+        <v>-4.99</v>
       </c>
       <c r="H5" s="8">
-        <v>0.89900000000000002</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="I5" s="7">
-        <v>-5</v>
-      </c>
-      <c r="J5" s="9">
-        <v>101.3</v>
+        <v>-10.3</v>
+      </c>
+      <c r="J5" s="7">
+        <v>-19.5</v>
       </c>
       <c r="K5" s="8">
-        <v>11.11</v>
+        <v>11.91</v>
       </c>
       <c r="L5" s="9">
-        <v>6.96</v>
+        <v>4.63</v>
       </c>
       <c r="M5" s="8">
-        <v>0.89900000000000002</v>
+        <v>0.80600000000000005</v>
       </c>
       <c r="N5" s="7">
-        <v>-5</v>
-      </c>
-      <c r="O5" s="9">
-        <v>101.3</v>
+        <v>-10.3</v>
+      </c>
+      <c r="O5" s="7">
+        <v>-19.5</v>
       </c>
       <c r="P5" s="8">
-        <v>11.11</v>
+        <v>11.91</v>
       </c>
       <c r="Q5" s="9">
-        <v>6.96</v>
+        <v>4.63</v>
       </c>
     </row>
     <row r="6" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A6" s="11">
-        <v>45931</v>
+        <v>45962</v>
       </c>
       <c r="B6" s="12">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C6" s="12">
-        <v>75</v>
+        <v>74.2</v>
       </c>
       <c r="D6" s="12">
-        <v>79.400000000000006</v>
+        <v>77.2</v>
       </c>
       <c r="E6" s="12">
-        <v>73.8</v>
+        <v>71.5</v>
       </c>
       <c r="F6" s="13">
-        <v>-3</v>
+        <v>-0.8</v>
       </c>
       <c r="G6" s="13">
-        <v>-3.85</v>
+        <v>-1.07</v>
       </c>
       <c r="H6" s="14">
-        <v>0.94699999999999995</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="I6" s="13">
-        <v>-42.5</v>
+        <v>-5</v>
       </c>
       <c r="J6" s="15">
-        <v>55.2</v>
+        <v>101.3</v>
       </c>
       <c r="K6" s="14">
-        <v>10.210000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="L6" s="15">
-        <v>2.72</v>
+        <v>6.96</v>
       </c>
       <c r="M6" s="14">
-        <v>0.94699999999999995</v>
+        <v>0.89900000000000002</v>
       </c>
       <c r="N6" s="13">
-        <v>-42.5</v>
+        <v>-5</v>
       </c>
       <c r="O6" s="15">
-        <v>55.2</v>
+        <v>101.3</v>
       </c>
       <c r="P6" s="14">
-        <v>10.210000000000001</v>
+        <v>11.11</v>
       </c>
       <c r="Q6" s="15">
-        <v>2.72</v>
+        <v>6.96</v>
       </c>
     </row>
     <row r="7" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
-        <v>45901</v>
+        <v>45931</v>
       </c>
       <c r="B7" s="6">
-        <v>73.5</v>
+        <v>78</v>
       </c>
       <c r="C7" s="6">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D7" s="6">
-        <v>78.400000000000006</v>
+        <v>79.400000000000006</v>
       </c>
       <c r="E7" s="6">
-        <v>71.400000000000006</v>
-      </c>
-      <c r="F7" s="9">
-        <v>4.5</v>
-      </c>
-      <c r="G7" s="9">
-        <v>6.12</v>
+        <v>73.8</v>
+      </c>
+      <c r="F7" s="7">
+        <v>-3</v>
+      </c>
+      <c r="G7" s="7">
+        <v>-3.85</v>
       </c>
       <c r="H7" s="8">
-        <v>1.65</v>
-      </c>
-      <c r="I7" s="9">
-        <v>0.26</v>
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="I7" s="7">
+        <v>-42.5</v>
       </c>
       <c r="J7" s="9">
-        <v>58.8</v>
+        <v>55.2</v>
       </c>
       <c r="K7" s="8">
-        <v>9.26</v>
-      </c>
-      <c r="L7" s="7">
-        <v>-0.7</v>
+        <v>10.210000000000001</v>
+      </c>
+      <c r="L7" s="9">
+        <v>2.72</v>
       </c>
       <c r="M7" s="8">
-        <v>1.65</v>
-      </c>
-      <c r="N7" s="9">
-        <v>0.26</v>
+        <v>0.94699999999999995</v>
+      </c>
+      <c r="N7" s="7">
+        <v>-42.5</v>
       </c>
       <c r="O7" s="9">
-        <v>58.8</v>
+        <v>55.2</v>
       </c>
       <c r="P7" s="8">
-        <v>9.26</v>
-      </c>
-      <c r="Q7" s="7">
-        <v>-0.7</v>
+        <v>10.210000000000001</v>
+      </c>
+      <c r="Q7" s="9">
+        <v>2.72</v>
       </c>
     </row>
     <row r="8" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A8" s="11">
-        <v>45870</v>
+        <v>45901</v>
       </c>
       <c r="B8" s="12">
-        <v>79</v>
+        <v>73.5</v>
       </c>
       <c r="C8" s="12">
-        <v>73.5</v>
+        <v>78</v>
       </c>
       <c r="D8" s="12">
-        <v>81.5</v>
+        <v>78.400000000000006</v>
       </c>
       <c r="E8" s="12">
-        <v>72.900000000000006</v>
-      </c>
-      <c r="F8" s="13">
-        <v>-5.5</v>
-      </c>
-      <c r="G8" s="13">
-        <v>-6.96</v>
+        <v>71.400000000000006</v>
+      </c>
+      <c r="F8" s="15">
+        <v>4.5</v>
+      </c>
+      <c r="G8" s="15">
+        <v>6.12</v>
       </c>
       <c r="H8" s="14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="I8" s="15">
-        <v>5.31</v>
+        <v>0.26</v>
       </c>
       <c r="J8" s="15">
-        <v>77.3</v>
+        <v>58.8</v>
       </c>
       <c r="K8" s="14">
-        <v>7.62</v>
+        <v>9.26</v>
       </c>
       <c r="L8" s="13">
-        <v>-8.15</v>
+        <v>-0.7</v>
       </c>
       <c r="M8" s="14">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="N8" s="15">
-        <v>5.31</v>
+        <v>0.26</v>
       </c>
       <c r="O8" s="15">
-        <v>77.3</v>
+        <v>58.8</v>
       </c>
       <c r="P8" s="14">
-        <v>7.62</v>
+        <v>9.26</v>
       </c>
       <c r="Q8" s="13">
-        <v>-8.15</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="9" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
-        <v>45839</v>
+        <v>45870</v>
       </c>
       <c r="B9" s="6">
-        <v>100.5</v>
+        <v>79</v>
       </c>
       <c r="C9" s="6">
-        <v>79</v>
+        <v>73.5</v>
       </c>
       <c r="D9" s="6">
-        <v>88.3</v>
+        <v>81.5</v>
       </c>
       <c r="E9" s="6">
-        <v>75.5</v>
+        <v>72.900000000000006</v>
       </c>
       <c r="F9" s="7">
-        <v>-21.5</v>
+        <v>-5.5</v>
       </c>
       <c r="G9" s="7">
-        <v>-21.39</v>
+        <v>-6.96</v>
       </c>
       <c r="H9" s="8">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="I9" s="9">
-        <v>58.5</v>
+        <v>5.31</v>
       </c>
       <c r="J9" s="9">
-        <v>55.2</v>
+        <v>77.3</v>
       </c>
       <c r="K9" s="8">
-        <v>5.97</v>
+        <v>7.62</v>
       </c>
       <c r="L9" s="7">
-        <v>-18.899999999999999</v>
+        <v>-8.15</v>
       </c>
       <c r="M9" s="8">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="N9" s="9">
-        <v>58.5</v>
+        <v>5.31</v>
       </c>
       <c r="O9" s="9">
-        <v>55.2</v>
+        <v>77.3</v>
       </c>
       <c r="P9" s="8">
-        <v>5.97</v>
+        <v>7.62</v>
       </c>
       <c r="Q9" s="7">
-        <v>-18.899999999999999</v>
+        <v>-8.15</v>
       </c>
     </row>
     <row r="10" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="11">
-        <v>45809</v>
+        <v>45839</v>
       </c>
       <c r="B10" s="12">
-        <v>88</v>
+        <v>100.5</v>
       </c>
       <c r="C10" s="12">
-        <v>100.5</v>
+        <v>79</v>
       </c>
       <c r="D10" s="12">
-        <v>102.5</v>
+        <v>88.3</v>
       </c>
       <c r="E10" s="12">
-        <v>86.8</v>
-      </c>
-      <c r="F10" s="15">
-        <v>12.5</v>
-      </c>
-      <c r="G10" s="15">
-        <v>14.2</v>
+        <v>75.5</v>
+      </c>
+      <c r="F10" s="13">
+        <v>-21.5</v>
+      </c>
+      <c r="G10" s="13">
+        <v>-21.39</v>
       </c>
       <c r="H10" s="14">
-        <v>0.98399999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="I10" s="15">
-        <v>23.9</v>
-      </c>
-      <c r="J10" s="13">
-        <v>-28.4</v>
+        <v>58.5</v>
+      </c>
+      <c r="J10" s="15">
+        <v>55.2</v>
       </c>
       <c r="K10" s="14">
-        <v>4.41</v>
+        <v>5.97</v>
       </c>
       <c r="L10" s="13">
-        <v>-30.6</v>
+        <v>-18.899999999999999</v>
       </c>
       <c r="M10" s="14">
-        <v>0.98399999999999999</v>
+        <v>1.56</v>
       </c>
       <c r="N10" s="15">
-        <v>23.9</v>
-      </c>
-      <c r="O10" s="13">
-        <v>-28.4</v>
+        <v>58.5</v>
+      </c>
+      <c r="O10" s="15">
+        <v>55.2</v>
       </c>
       <c r="P10" s="14">
-        <v>4.41</v>
+        <v>5.97</v>
       </c>
       <c r="Q10" s="13">
-        <v>-30.6</v>
+        <v>-18.899999999999999</v>
       </c>
     </row>
     <row r="11" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
-        <v>45778</v>
+        <v>45809</v>
       </c>
       <c r="B11" s="6">
-        <v>89.3</v>
+        <v>88</v>
       </c>
       <c r="C11" s="6">
-        <v>88</v>
+        <v>100.5</v>
       </c>
       <c r="D11" s="6">
-        <v>94.3</v>
+        <v>102.5</v>
       </c>
       <c r="E11" s="6">
-        <v>86</v>
-      </c>
-      <c r="F11" s="7">
-        <v>-1.3</v>
-      </c>
-      <c r="G11" s="7">
-        <v>-1.46</v>
+        <v>86.8</v>
+      </c>
+      <c r="F11" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="G11" s="9">
+        <v>14.2</v>
       </c>
       <c r="H11" s="8">
-        <v>0.79500000000000004</v>
-      </c>
-      <c r="I11" s="7">
-        <v>-13</v>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="I11" s="9">
+        <v>23.9</v>
       </c>
       <c r="J11" s="7">
-        <v>-40.200000000000003</v>
+        <v>-28.4</v>
       </c>
       <c r="K11" s="8">
-        <v>3.43</v>
+        <v>4.41</v>
       </c>
       <c r="L11" s="7">
-        <v>-31.2</v>
+        <v>-30.6</v>
       </c>
       <c r="M11" s="8">
-        <v>0.79500000000000004</v>
-      </c>
-      <c r="N11" s="7">
-        <v>-13</v>
+        <v>0.98399999999999999</v>
+      </c>
+      <c r="N11" s="9">
+        <v>23.9</v>
       </c>
       <c r="O11" s="7">
-        <v>-40.200000000000003</v>
+        <v>-28.4</v>
       </c>
       <c r="P11" s="8">
-        <v>3.43</v>
+        <v>4.41</v>
       </c>
       <c r="Q11" s="7">
-        <v>-31.2</v>
+        <v>-30.6</v>
       </c>
     </row>
     <row r="12" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11">
-        <v>45748</v>
+        <v>45778</v>
       </c>
       <c r="B12" s="12">
-        <v>92.5</v>
+        <v>89.3</v>
       </c>
       <c r="C12" s="12">
-        <v>89.3</v>
+        <v>88</v>
       </c>
       <c r="D12" s="12">
-        <v>95.3</v>
+        <v>94.3</v>
       </c>
       <c r="E12" s="12">
-        <v>77.3</v>
+        <v>86</v>
       </c>
       <c r="F12" s="13">
-        <v>-3.2</v>
+        <v>-1.3</v>
       </c>
       <c r="G12" s="13">
-        <v>-3.46</v>
+        <v>-1.46</v>
       </c>
       <c r="H12" s="14">
-        <v>0.91300000000000003</v>
-      </c>
-      <c r="I12" s="15">
-        <v>30.9</v>
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="I12" s="13">
+        <v>-13</v>
       </c>
       <c r="J12" s="13">
-        <v>-24.7</v>
+        <v>-40.200000000000003</v>
       </c>
       <c r="K12" s="14">
-        <v>2.64</v>
+        <v>3.43</v>
       </c>
       <c r="L12" s="13">
-        <v>-28</v>
+        <v>-31.2</v>
       </c>
       <c r="M12" s="14">
-        <v>0.91300000000000003</v>
-      </c>
-      <c r="N12" s="15">
-        <v>30.9</v>
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="N12" s="13">
+        <v>-13</v>
       </c>
       <c r="O12" s="13">
-        <v>-24.7</v>
+        <v>-40.200000000000003</v>
       </c>
       <c r="P12" s="14">
-        <v>2.64</v>
+        <v>3.43</v>
       </c>
       <c r="Q12" s="13">
-        <v>-28</v>
+        <v>-31.2</v>
       </c>
     </row>
     <row r="13" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
-        <v>45717</v>
+        <v>45748</v>
       </c>
       <c r="B13" s="6">
-        <v>98.8</v>
+        <v>92.5</v>
       </c>
       <c r="C13" s="6">
-        <v>92.5</v>
+        <v>89.3</v>
       </c>
       <c r="D13" s="6">
-        <v>116</v>
+        <v>95.3</v>
       </c>
       <c r="E13" s="6">
-        <v>92.2</v>
+        <v>77.3</v>
       </c>
       <c r="F13" s="7">
-        <v>-6.3</v>
+        <v>-3.2</v>
       </c>
       <c r="G13" s="7">
-        <v>-6.38</v>
+        <v>-3.46</v>
       </c>
       <c r="H13" s="8">
-        <v>0.69799999999999995</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="I13" s="9">
-        <v>46.4</v>
+        <v>30.9</v>
       </c>
       <c r="J13" s="7">
-        <v>-40</v>
+        <v>-24.7</v>
       </c>
       <c r="K13" s="8">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="L13" s="7">
-        <v>-29.6</v>
+        <v>-28</v>
       </c>
       <c r="M13" s="8">
-        <v>0.69799999999999995</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="N13" s="9">
-        <v>46.4</v>
+        <v>30.9</v>
       </c>
       <c r="O13" s="7">
-        <v>-40</v>
+        <v>-24.7</v>
       </c>
       <c r="P13" s="8">
-        <v>1.72</v>
+        <v>2.64</v>
       </c>
       <c r="Q13" s="7">
-        <v>-29.6</v>
+        <v>-28</v>
       </c>
     </row>
     <row r="14" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A14" s="11">
-        <v>45689</v>
+        <v>45717</v>
       </c>
       <c r="B14" s="12">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="C14" s="12">
-        <v>98.8</v>
+        <v>92.5</v>
       </c>
       <c r="D14" s="12">
-        <v>104</v>
+        <v>116</v>
       </c>
       <c r="E14" s="12">
-        <v>95.8</v>
-      </c>
-      <c r="F14" s="15">
-        <v>0.6</v>
-      </c>
-      <c r="G14" s="15">
-        <v>0.61</v>
+        <v>92.2</v>
+      </c>
+      <c r="F14" s="13">
+        <v>-6.3</v>
+      </c>
+      <c r="G14" s="13">
+        <v>-6.38</v>
       </c>
       <c r="H14" s="14">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="I14" s="13">
-        <v>-12.9</v>
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="I14" s="15">
+        <v>46.4</v>
       </c>
       <c r="J14" s="13">
-        <v>-30.8</v>
+        <v>-40</v>
       </c>
       <c r="K14" s="14">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="L14" s="13">
-        <v>-20.100000000000001</v>
+        <v>-29.6</v>
       </c>
       <c r="M14" s="14">
-        <v>0.47599999999999998</v>
-      </c>
-      <c r="N14" s="13">
-        <v>-12.9</v>
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="N14" s="15">
+        <v>46.4</v>
       </c>
       <c r="O14" s="13">
-        <v>-30.8</v>
+        <v>-40</v>
       </c>
       <c r="P14" s="14">
-        <v>1.02</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" s="13">
-        <v>-20.100000000000001</v>
+        <v>-29.6</v>
       </c>
     </row>
     <row r="15" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
-        <v>45658</v>
+        <v>45689</v>
       </c>
       <c r="B15" s="6">
-        <v>82</v>
+        <v>98.2</v>
       </c>
       <c r="C15" s="6">
-        <v>98.2</v>
+        <v>98.8</v>
       </c>
       <c r="D15" s="6">
-        <v>99.9</v>
+        <v>104</v>
       </c>
       <c r="E15" s="6">
-        <v>79.7</v>
+        <v>95.8</v>
       </c>
       <c r="F15" s="9">
-        <v>16.2</v>
+        <v>0.6</v>
       </c>
       <c r="G15" s="9">
-        <v>19.760000000000002</v>
+        <v>0.61</v>
       </c>
       <c r="H15" s="8">
-        <v>0.54700000000000004</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="I15" s="7">
-        <v>-45.4</v>
+        <v>-12.9</v>
       </c>
       <c r="J15" s="7">
-        <v>-7.79</v>
+        <v>-30.8</v>
       </c>
       <c r="K15" s="8">
-        <v>0.54700000000000004</v>
+        <v>1.02</v>
       </c>
       <c r="L15" s="7">
-        <v>-7.79</v>
+        <v>-20.100000000000001</v>
       </c>
       <c r="M15" s="8">
-        <v>0.54700000000000004</v>
+        <v>0.47599999999999998</v>
       </c>
       <c r="N15" s="7">
-        <v>-45.4</v>
+        <v>-12.9</v>
       </c>
       <c r="O15" s="7">
-        <v>-7.79</v>
+        <v>-30.8</v>
       </c>
       <c r="P15" s="8">
-        <v>0.54700000000000004</v>
+        <v>1.02</v>
       </c>
       <c r="Q15" s="7">
-        <v>-7.79</v>
+        <v>-20.100000000000001</v>
       </c>
     </row>
     <row r="16" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="11">
-        <v>45627</v>
+        <v>45658</v>
       </c>
       <c r="B16" s="12">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="C16" s="12">
-        <v>82</v>
+        <v>98.2</v>
       </c>
       <c r="D16" s="12">
-        <v>95</v>
+        <v>99.9</v>
       </c>
       <c r="E16" s="12">
-        <v>79</v>
-      </c>
-      <c r="F16" s="13">
-        <v>-6</v>
-      </c>
-      <c r="G16" s="13">
-        <v>-6.82</v>
+        <v>79.7</v>
+      </c>
+      <c r="F16" s="15">
+        <v>16.2</v>
+      </c>
+      <c r="G16" s="15">
+        <v>19.760000000000002</v>
       </c>
       <c r="H16" s="14">
-        <v>1</v>
-      </c>
-      <c r="I16" s="15">
-        <v>124.3</v>
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="I16" s="13">
+        <v>-45.4</v>
       </c>
       <c r="J16" s="13">
-        <v>-3.21</v>
+        <v>-7.79</v>
       </c>
       <c r="K16" s="14">
-        <v>11.39</v>
-      </c>
-      <c r="L16" s="15">
-        <v>19.399999999999999</v>
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="L16" s="13">
+        <v>-7.79</v>
       </c>
       <c r="M16" s="14">
-        <v>1</v>
-      </c>
-      <c r="N16" s="15">
-        <v>124.3</v>
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="N16" s="13">
+        <v>-45.4</v>
       </c>
       <c r="O16" s="13">
-        <v>-3.21</v>
+        <v>-7.79</v>
       </c>
       <c r="P16" s="14">
-        <v>11.39</v>
-      </c>
-      <c r="Q16" s="15">
-        <v>19.399999999999999</v>
+        <v>0.54700000000000004</v>
+      </c>
+      <c r="Q16" s="13">
+        <v>-7.79</v>
       </c>
     </row>
     <row r="17" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
-        <v>45597</v>
+        <v>45627</v>
       </c>
       <c r="B17" s="6">
-        <v>106.5</v>
+        <v>88</v>
       </c>
       <c r="C17" s="6">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="D17" s="6">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="E17" s="6">
-        <v>86.7</v>
+        <v>79</v>
       </c>
       <c r="F17" s="7">
-        <v>-18.5</v>
+        <v>-6</v>
       </c>
       <c r="G17" s="7">
-        <v>-17.37</v>
+        <v>-6.82</v>
       </c>
       <c r="H17" s="8">
-        <v>0.44700000000000001</v>
-      </c>
-      <c r="I17" s="7">
-        <v>-26.8</v>
-      </c>
-      <c r="J17" s="9">
-        <v>216.6</v>
+        <v>1</v>
+      </c>
+      <c r="I17" s="9">
+        <v>124.3</v>
+      </c>
+      <c r="J17" s="7">
+        <v>-3.21</v>
       </c>
       <c r="K17" s="8">
-        <v>10.38</v>
+        <v>11.39</v>
       </c>
       <c r="L17" s="9">
-        <v>22.2</v>
+        <v>19.399999999999999</v>
       </c>
       <c r="M17" s="8">
-        <v>0.44700000000000001</v>
-      </c>
-      <c r="N17" s="7">
-        <v>-26.8</v>
-      </c>
-      <c r="O17" s="9">
-        <v>216.6</v>
+        <v>1</v>
+      </c>
+      <c r="N17" s="9">
+        <v>124.3</v>
+      </c>
+      <c r="O17" s="7">
+        <v>-3.21</v>
       </c>
       <c r="P17" s="8">
-        <v>10.38</v>
+        <v>11.39</v>
       </c>
       <c r="Q17" s="9">
-        <v>22.2</v>
+        <v>19.399999999999999</v>
       </c>
     </row>
     <row r="18" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="11">
-        <v>45566</v>
+        <v>45597</v>
       </c>
       <c r="B18" s="12">
-        <v>118</v>
+        <v>106.5</v>
       </c>
       <c r="C18" s="12">
-        <v>106.5</v>
+        <v>88</v>
       </c>
       <c r="D18" s="12">
-        <v>121.5</v>
+        <v>120</v>
       </c>
       <c r="E18" s="12">
-        <v>102</v>
+        <v>86.7</v>
       </c>
       <c r="F18" s="13">
-        <v>-11.5</v>
+        <v>-18.5</v>
       </c>
       <c r="G18" s="13">
-        <v>-9.75</v>
+        <v>-17.37</v>
       </c>
       <c r="H18" s="14">
-        <v>0.61</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="I18" s="13">
-        <v>-41.2</v>
-      </c>
-      <c r="J18" s="13">
-        <v>-42</v>
+        <v>-26.8</v>
+      </c>
+      <c r="J18" s="15">
+        <v>216.6</v>
       </c>
       <c r="K18" s="14">
-        <v>9.94</v>
+        <v>10.38</v>
       </c>
       <c r="L18" s="15">
-        <v>18.899999999999999</v>
+        <v>22.2</v>
       </c>
       <c r="M18" s="14">
-        <v>0.61</v>
+        <v>0.44700000000000001</v>
       </c>
       <c r="N18" s="13">
-        <v>-41.2</v>
-      </c>
-      <c r="O18" s="13">
-        <v>-42</v>
+        <v>-26.8</v>
+      </c>
+      <c r="O18" s="15">
+        <v>216.6</v>
       </c>
       <c r="P18" s="14">
-        <v>9.94</v>
+        <v>10.38</v>
       </c>
       <c r="Q18" s="15">
-        <v>18.899999999999999</v>
+        <v>22.2</v>
       </c>
     </row>
     <row r="19" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
-        <v>45536</v>
+        <v>45566</v>
       </c>
       <c r="B19" s="6">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="C19" s="6">
-        <v>118</v>
+        <v>106.5</v>
       </c>
       <c r="D19" s="6">
-        <v>154</v>
+        <v>121.5</v>
       </c>
       <c r="E19" s="6">
-        <v>116</v>
+        <v>102</v>
       </c>
       <c r="F19" s="7">
-        <v>-27</v>
+        <v>-11.5</v>
       </c>
       <c r="G19" s="7">
-        <v>-18.62</v>
+        <v>-9.75</v>
       </c>
       <c r="H19" s="8">
-        <v>1.04</v>
-      </c>
-      <c r="I19" s="9">
-        <v>12</v>
+        <v>0.61</v>
+      </c>
+      <c r="I19" s="7">
+        <v>-41.2</v>
       </c>
       <c r="J19" s="7">
-        <v>-36.5</v>
+        <v>-42</v>
       </c>
       <c r="K19" s="8">
-        <v>9.33</v>
+        <v>9.94</v>
       </c>
       <c r="L19" s="9">
-        <v>27.6</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="M19" s="8">
-        <v>1.04</v>
-      </c>
-      <c r="N19" s="9">
-        <v>12</v>
+        <v>0.61</v>
+      </c>
+      <c r="N19" s="7">
+        <v>-41.2</v>
       </c>
       <c r="O19" s="7">
-        <v>-36.5</v>
+        <v>-42</v>
       </c>
       <c r="P19" s="8">
-        <v>9.33</v>
+        <v>9.94</v>
       </c>
       <c r="Q19" s="9">
-        <v>27.6</v>
+        <v>18.899999999999999</v>
       </c>
     </row>
     <row r="20" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A20" s="11">
-        <v>45505</v>
+        <v>45536</v>
       </c>
       <c r="B20" s="12">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="C20" s="12">
-        <v>145</v>
+        <v>118</v>
       </c>
       <c r="D20" s="12">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E20" s="12">
-        <v>94.1</v>
-      </c>
-      <c r="F20" s="15">
-        <v>37</v>
-      </c>
-      <c r="G20" s="15">
-        <v>34.26</v>
+        <v>116</v>
+      </c>
+      <c r="F20" s="13">
+        <v>-27</v>
+      </c>
+      <c r="G20" s="13">
+        <v>-18.62</v>
       </c>
       <c r="H20" s="14">
-        <v>0.92600000000000005</v>
-      </c>
-      <c r="I20" s="13">
-        <v>-7.84</v>
+        <v>1.04</v>
+      </c>
+      <c r="I20" s="15">
+        <v>12</v>
       </c>
       <c r="J20" s="13">
-        <v>-34.200000000000003</v>
+        <v>-36.5</v>
       </c>
       <c r="K20" s="14">
-        <v>8.2899999999999991</v>
+        <v>9.33</v>
       </c>
       <c r="L20" s="15">
-        <v>46.1</v>
+        <v>27.6</v>
       </c>
       <c r="M20" s="14">
-        <v>0.92600000000000005</v>
-      </c>
-      <c r="N20" s="13">
-        <v>-7.84</v>
+        <v>1.04</v>
+      </c>
+      <c r="N20" s="15">
+        <v>12</v>
       </c>
       <c r="O20" s="13">
-        <v>-34.200000000000003</v>
+        <v>-36.5</v>
       </c>
       <c r="P20" s="14">
-        <v>8.2899999999999991</v>
+        <v>9.33</v>
       </c>
       <c r="Q20" s="15">
-        <v>46.1</v>
+        <v>27.6</v>
       </c>
     </row>
     <row r="21" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
-        <v>45474</v>
+        <v>45505</v>
       </c>
       <c r="B21" s="6">
-        <v>124.5</v>
+        <v>108</v>
       </c>
       <c r="C21" s="6">
-        <v>108</v>
+        <v>145</v>
       </c>
       <c r="D21" s="6">
-        <v>140</v>
+        <v>161</v>
       </c>
       <c r="E21" s="6">
-        <v>103.5</v>
-      </c>
-      <c r="F21" s="7">
-        <v>-16.5</v>
-      </c>
-      <c r="G21" s="7">
-        <v>-13.25</v>
+        <v>94.1</v>
+      </c>
+      <c r="F21" s="9">
+        <v>37</v>
+      </c>
+      <c r="G21" s="9">
+        <v>34.26</v>
       </c>
       <c r="H21" s="8">
-        <v>1</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="I21" s="7">
-        <v>-26.8</v>
+        <v>-7.84</v>
       </c>
       <c r="J21" s="7">
-        <v>-28.6</v>
+        <v>-34.200000000000003</v>
       </c>
       <c r="K21" s="8">
-        <v>7.37</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="L21" s="9">
-        <v>72.599999999999994</v>
+        <v>46.1</v>
       </c>
       <c r="M21" s="8">
-        <v>1</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="N21" s="7">
-        <v>-26.8</v>
+        <v>-7.84</v>
       </c>
       <c r="O21" s="7">
-        <v>-28.6</v>
+        <v>-34.200000000000003</v>
       </c>
       <c r="P21" s="8">
-        <v>7.37</v>
+        <v>8.2899999999999991</v>
       </c>
       <c r="Q21" s="9">
-        <v>72.599999999999994</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="22" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="11">
-        <v>45444</v>
+        <v>45474</v>
       </c>
       <c r="B22" s="12">
-        <v>102.5</v>
+        <v>124.5</v>
       </c>
       <c r="C22" s="12">
-        <v>124.5</v>
+        <v>108</v>
       </c>
       <c r="D22" s="12">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="E22" s="12">
-        <v>100</v>
-      </c>
-      <c r="F22" s="15">
-        <v>22</v>
-      </c>
-      <c r="G22" s="15">
-        <v>21.46</v>
+        <v>103.5</v>
+      </c>
+      <c r="F22" s="13">
+        <v>-16.5</v>
+      </c>
+      <c r="G22" s="13">
+        <v>-13.25</v>
       </c>
       <c r="H22" s="14">
-        <v>1.37</v>
-      </c>
-      <c r="I22" s="15">
-        <v>3.42</v>
-      </c>
-      <c r="J22" s="15">
-        <v>50.6</v>
+        <v>1</v>
+      </c>
+      <c r="I22" s="13">
+        <v>-26.8</v>
+      </c>
+      <c r="J22" s="13">
+        <v>-28.6</v>
       </c>
       <c r="K22" s="14">
-        <v>6.36</v>
+        <v>7.37</v>
       </c>
       <c r="L22" s="15">
-        <v>122.5</v>
+        <v>72.599999999999994</v>
       </c>
       <c r="M22" s="14">
-        <v>1.37</v>
-      </c>
-      <c r="N22" s="15">
-        <v>3.42</v>
-      </c>
-      <c r="O22" s="15">
-        <v>50.6</v>
+        <v>1</v>
+      </c>
+      <c r="N22" s="13">
+        <v>-26.8</v>
+      </c>
+      <c r="O22" s="13">
+        <v>-28.6</v>
       </c>
       <c r="P22" s="14">
-        <v>6.36</v>
+        <v>7.37</v>
       </c>
       <c r="Q22" s="15">
-        <v>122.5</v>
+        <v>72.599999999999994</v>
       </c>
     </row>
     <row r="23" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
-        <v>45413</v>
+        <v>45444</v>
       </c>
       <c r="B23" s="6">
-        <v>106</v>
+        <v>102.5</v>
       </c>
       <c r="C23" s="6">
-        <v>102.5</v>
+        <v>124.5</v>
       </c>
       <c r="D23" s="6">
-        <v>124.5</v>
+        <v>126</v>
       </c>
       <c r="E23" s="6">
-        <v>99.1</v>
-      </c>
-      <c r="F23" s="7">
-        <v>-3.5</v>
-      </c>
-      <c r="G23" s="7">
-        <v>-3.3</v>
+        <v>100</v>
+      </c>
+      <c r="F23" s="9">
+        <v>22</v>
+      </c>
+      <c r="G23" s="9">
+        <v>21.46</v>
       </c>
       <c r="H23" s="8">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="I23" s="9">
-        <v>9.41</v>
+        <v>3.42</v>
       </c>
       <c r="J23" s="9">
-        <v>120</v>
+        <v>50.6</v>
       </c>
       <c r="K23" s="8">
-        <v>4.99</v>
+        <v>6.36</v>
       </c>
       <c r="L23" s="9">
-        <v>156.19999999999999</v>
+        <v>122.5</v>
       </c>
       <c r="M23" s="8">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="N23" s="9">
-        <v>9.41</v>
+        <v>3.42</v>
       </c>
       <c r="O23" s="9">
-        <v>120</v>
+        <v>50.6</v>
       </c>
       <c r="P23" s="8">
-        <v>4.99</v>
+        <v>6.36</v>
       </c>
       <c r="Q23" s="9">
-        <v>156.19999999999999</v>
+        <v>122.5</v>
       </c>
     </row>
     <row r="24" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A24" s="11">
-        <v>45383</v>
+        <v>45413</v>
       </c>
       <c r="B24" s="12">
-        <v>90.9</v>
+        <v>106</v>
       </c>
       <c r="C24" s="12">
-        <v>106</v>
+        <v>102.5</v>
       </c>
       <c r="D24" s="12">
-        <v>118.5</v>
+        <v>124.5</v>
       </c>
       <c r="E24" s="12">
-        <v>86</v>
-      </c>
-      <c r="F24" s="15">
-        <v>15.1</v>
-      </c>
-      <c r="G24" s="15">
-        <v>16.61</v>
+        <v>99.1</v>
+      </c>
+      <c r="F24" s="13">
+        <v>-3.5</v>
+      </c>
+      <c r="G24" s="13">
+        <v>-3.3</v>
       </c>
       <c r="H24" s="14">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="I24" s="15">
-        <v>4.42</v>
+        <v>9.41</v>
       </c>
       <c r="J24" s="15">
-        <v>190.2</v>
+        <v>120</v>
       </c>
       <c r="K24" s="14">
-        <v>3.66</v>
+        <v>4.99</v>
       </c>
       <c r="L24" s="15">
-        <v>172.5</v>
+        <v>156.19999999999999</v>
       </c>
       <c r="M24" s="14">
-        <v>1.21</v>
+        <v>1.33</v>
       </c>
       <c r="N24" s="15">
-        <v>4.42</v>
+        <v>9.41</v>
       </c>
       <c r="O24" s="15">
-        <v>190.2</v>
+        <v>120</v>
       </c>
       <c r="P24" s="14">
-        <v>3.66</v>
+        <v>4.99</v>
       </c>
       <c r="Q24" s="15">
-        <v>172.5</v>
+        <v>156.19999999999999</v>
       </c>
     </row>
     <row r="25" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
-        <v>45352</v>
+        <v>45383</v>
       </c>
       <c r="B25" s="6">
-        <v>85</v>
+        <v>90.9</v>
       </c>
       <c r="C25" s="6">
-        <v>90.9</v>
+        <v>106</v>
       </c>
       <c r="D25" s="6">
-        <v>91.4</v>
+        <v>118.5</v>
       </c>
       <c r="E25" s="6">
-        <v>81.7</v>
+        <v>86</v>
       </c>
       <c r="F25" s="9">
-        <v>5.9</v>
+        <v>15.1</v>
       </c>
       <c r="G25" s="9">
-        <v>6.94</v>
+        <v>16.61</v>
       </c>
       <c r="H25" s="8">
-        <v>1.1599999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="I25" s="9">
-        <v>68.8</v>
+        <v>4.42</v>
       </c>
       <c r="J25" s="9">
-        <v>193.7</v>
+        <v>190.2</v>
       </c>
       <c r="K25" s="8">
-        <v>2.44</v>
+        <v>3.66</v>
       </c>
       <c r="L25" s="9">
-        <v>164.6</v>
+        <v>172.5</v>
       </c>
       <c r="M25" s="8">
-        <v>1.1599999999999999</v>
+        <v>1.21</v>
       </c>
       <c r="N25" s="9">
-        <v>68.8</v>
+        <v>4.42</v>
       </c>
       <c r="O25" s="9">
-        <v>193.7</v>
+        <v>190.2</v>
       </c>
       <c r="P25" s="8">
-        <v>2.44</v>
+        <v>3.66</v>
       </c>
       <c r="Q25" s="9">
-        <v>164.6</v>
+        <v>172.5</v>
       </c>
     </row>
     <row r="26" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A26" s="11">
-        <v>45323</v>
+        <v>45352</v>
       </c>
       <c r="B26" s="12">
         <v>85</v>
       </c>
       <c r="C26" s="12">
-        <v>85</v>
+        <v>90.9</v>
       </c>
       <c r="D26" s="12">
-        <v>85</v>
+        <v>91.4</v>
       </c>
       <c r="E26" s="12">
-        <v>80.8</v>
-      </c>
-      <c r="F26" s="14">
-        <v>0</v>
-      </c>
-      <c r="G26" s="14">
-        <v>0</v>
+        <v>81.7</v>
+      </c>
+      <c r="F26" s="15">
+        <v>5.9</v>
+      </c>
+      <c r="G26" s="15">
+        <v>6.94</v>
       </c>
       <c r="H26" s="14">
-        <v>0.68899999999999995</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="I26" s="15">
-        <v>16</v>
+        <v>68.8</v>
       </c>
       <c r="J26" s="15">
-        <v>100.1</v>
+        <v>193.7</v>
       </c>
       <c r="K26" s="14">
-        <v>1.28</v>
+        <v>2.44</v>
       </c>
       <c r="L26" s="15">
-        <v>142.69999999999999</v>
+        <v>164.6</v>
       </c>
       <c r="M26" s="14">
-        <v>0.68899999999999995</v>
+        <v>1.1599999999999999</v>
       </c>
       <c r="N26" s="15">
-        <v>16</v>
+        <v>68.8</v>
       </c>
       <c r="O26" s="15">
-        <v>100.1</v>
+        <v>193.7</v>
       </c>
       <c r="P26" s="14">
-        <v>1.28</v>
+        <v>2.44</v>
       </c>
       <c r="Q26" s="15">
-        <v>142.69999999999999</v>
+        <v>164.6</v>
       </c>
     </row>
     <row r="27" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
-        <v>45292</v>
+        <v>45323</v>
       </c>
       <c r="B27" s="6">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C27" s="6">
         <v>85</v>
       </c>
       <c r="D27" s="6">
-        <v>91.5</v>
+        <v>85</v>
       </c>
       <c r="E27" s="6">
-        <v>80.099999999999994</v>
-      </c>
-      <c r="F27" s="7">
-        <v>-1</v>
-      </c>
-      <c r="G27" s="7">
-        <v>-1.1599999999999999</v>
+        <v>80.8</v>
+      </c>
+      <c r="F27" s="8">
+        <v>0</v>
+      </c>
+      <c r="G27" s="8">
+        <v>0</v>
       </c>
       <c r="H27" s="8">
-        <v>0.59399999999999997</v>
-      </c>
-      <c r="I27" s="7">
-        <v>-42.6</v>
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="I27" s="9">
+        <v>16</v>
       </c>
       <c r="J27" s="9">
-        <v>222.2</v>
+        <v>100.1</v>
       </c>
       <c r="K27" s="8">
-        <v>0.59399999999999997</v>
+        <v>1.28</v>
       </c>
       <c r="L27" s="9">
-        <v>222.2</v>
+        <v>142.69999999999999</v>
       </c>
       <c r="M27" s="8">
-        <v>0.59399999999999997</v>
-      </c>
-      <c r="N27" s="7">
-        <v>-42.6</v>
+        <v>0.68899999999999995</v>
+      </c>
+      <c r="N27" s="9">
+        <v>16</v>
       </c>
       <c r="O27" s="9">
-        <v>222.2</v>
+        <v>100.1</v>
       </c>
       <c r="P27" s="8">
-        <v>0.59399999999999997</v>
+        <v>1.28</v>
       </c>
       <c r="Q27" s="9">
-        <v>222.2</v>
+        <v>142.69999999999999</v>
       </c>
     </row>
     <row r="28" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11">
-        <v>45261</v>
-      </c>
-      <c r="B28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="F28" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>17</v>
+        <v>45292</v>
+      </c>
+      <c r="B28" s="12">
+        <v>86</v>
+      </c>
+      <c r="C28" s="12">
+        <v>85</v>
+      </c>
+      <c r="D28" s="12">
+        <v>91.5</v>
+      </c>
+      <c r="E28" s="12">
+        <v>80.099999999999994</v>
+      </c>
+      <c r="F28" s="13">
+        <v>-1</v>
+      </c>
+      <c r="G28" s="13">
+        <v>-1.1599999999999999</v>
       </c>
       <c r="H28" s="14">
-        <v>1.04</v>
-      </c>
-      <c r="I28" s="15">
-        <v>633.6</v>
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="I28" s="13">
+        <v>-42.6</v>
       </c>
       <c r="J28" s="15">
-        <v>174.5</v>
+        <v>222.2</v>
       </c>
       <c r="K28" s="14">
-        <v>9.5299999999999994</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="L28" s="15">
-        <v>67.599999999999994</v>
+        <v>222.2</v>
       </c>
       <c r="M28" s="14">
-        <v>1.04</v>
-      </c>
-      <c r="N28" s="15">
-        <v>633.6</v>
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="N28" s="13">
+        <v>-42.6</v>
       </c>
       <c r="O28" s="15">
-        <v>174.5</v>
+        <v>222.2</v>
       </c>
       <c r="P28" s="14">
-        <v>9.5299999999999994</v>
+        <v>0.59399999999999997</v>
       </c>
       <c r="Q28" s="15">
-        <v>67.599999999999994</v>
+        <v>222.2</v>
       </c>
     </row>
     <row r="29" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
-        <v>45231</v>
+        <v>45261</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>17</v>
@@ -2717,39 +2717,39 @@
         <v>17</v>
       </c>
       <c r="H29" s="8">
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="I29" s="7">
-        <v>-86.6</v>
+        <v>1.04</v>
+      </c>
+      <c r="I29" s="9">
+        <v>633.6</v>
       </c>
       <c r="J29" s="9">
-        <v>2503.3000000000002</v>
+        <v>174.5</v>
       </c>
       <c r="K29" s="8">
-        <v>8.5</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="L29" s="9">
-        <v>60</v>
+        <v>67.599999999999994</v>
       </c>
       <c r="M29" s="8">
-        <v>0.14099999999999999</v>
-      </c>
-      <c r="N29" s="7">
-        <v>-86.6</v>
+        <v>1.04</v>
+      </c>
+      <c r="N29" s="9">
+        <v>633.6</v>
       </c>
       <c r="O29" s="9">
-        <v>2503.3000000000002</v>
+        <v>174.5</v>
       </c>
       <c r="P29" s="8">
-        <v>8.5</v>
+        <v>9.5299999999999994</v>
       </c>
       <c r="Q29" s="9">
-        <v>60</v>
+        <v>67.599999999999994</v>
       </c>
     </row>
     <row r="30" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="11">
-        <v>45200</v>
+        <v>45231</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>17</v>
@@ -2770,39 +2770,39 @@
         <v>17</v>
       </c>
       <c r="H30" s="14">
-        <v>1.05</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="I30" s="13">
-        <v>-35.6</v>
+        <v>-86.6</v>
       </c>
       <c r="J30" s="15">
-        <v>21.9</v>
+        <v>2503.3000000000002</v>
       </c>
       <c r="K30" s="14">
-        <v>8.36</v>
+        <v>8.5</v>
       </c>
       <c r="L30" s="15">
-        <v>57.5</v>
+        <v>60</v>
       </c>
       <c r="M30" s="14">
-        <v>1.05</v>
+        <v>0.14099999999999999</v>
       </c>
       <c r="N30" s="13">
-        <v>-35.6</v>
+        <v>-86.6</v>
       </c>
       <c r="O30" s="15">
-        <v>21.9</v>
+        <v>2503.3000000000002</v>
       </c>
       <c r="P30" s="14">
-        <v>8.36</v>
+        <v>8.5</v>
       </c>
       <c r="Q30" s="15">
-        <v>57.5</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:17" s="4" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
-        <v>45170</v>
+        <v>45200</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>17</v>
@@ -2823,33 +2823,86 @@
         <v>17</v>
       </c>
       <c r="H31" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="I31" s="7">
+        <v>-35.6</v>
+      </c>
+      <c r="J31" s="9">
+        <v>21.9</v>
+      </c>
+      <c r="K31" s="8">
+        <v>8.36</v>
+      </c>
+      <c r="L31" s="9">
+        <v>57.5</v>
+      </c>
+      <c r="M31" s="8">
+        <v>1.05</v>
+      </c>
+      <c r="N31" s="7">
+        <v>-35.6</v>
+      </c>
+      <c r="O31" s="9">
+        <v>21.9</v>
+      </c>
+      <c r="P31" s="8">
+        <v>8.36</v>
+      </c>
+      <c r="Q31" s="9">
+        <v>57.5</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="11">
+        <v>45170</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="F32" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="G32" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="H32" s="14">
         <v>1.63</v>
       </c>
-      <c r="I31" s="8" t="s">
+      <c r="I32" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="J31" s="9">
+      <c r="J32" s="15">
         <v>168.9</v>
       </c>
-      <c r="K31" s="8">
+      <c r="K32" s="14">
         <v>7.31</v>
       </c>
-      <c r="L31" s="9">
+      <c r="L32" s="15">
         <v>64.5</v>
       </c>
-      <c r="M31" s="8">
+      <c r="M32" s="14">
         <v>1.63</v>
       </c>
-      <c r="N31" s="8" t="s">
+      <c r="N32" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="O31" s="9">
+      <c r="O32" s="15">
         <v>168.9</v>
       </c>
-      <c r="P31" s="8">
+      <c r="P32" s="14">
         <v>7.31</v>
       </c>
-      <c r="Q31" s="9">
+      <c r="Q32" s="15">
         <v>64.5</v>
       </c>
     </row>
